--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/allenmehr/Documents/GitHub/allen-mehr/capabilities/marginal-analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8CB5059-B9A7-DB42-BE2A-9592420592C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7278C96-8A4E-FC47-9D8A-A1067E752D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{BDFB547A-7CF5-5D46-A116-A51B8B0DF0D0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20420" activeTab="3" xr2:uid="{BDFB547A-7CF5-5D46-A116-A51B8B0DF0D0}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="2" r:id="rId1"/>
@@ -94,6 +94,65 @@
     <definedName name="revenue_total">Mix!$E$25</definedName>
     <definedName name="season_profit">Mix!$B$35</definedName>
     <definedName name="season_weeks">Inputs!$B$5</definedName>
+    <definedName name="solver_adj" localSheetId="3" hidden="1">Mix!$B$5:$B$7</definedName>
+    <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="3" hidden="1">Mix!$B$5:$B$7</definedName>
+    <definedName name="solver_lhs10" localSheetId="3" hidden="1">Mix!$B$17</definedName>
+    <definedName name="solver_lhs11" localSheetId="3" hidden="1">Mix!$B$5</definedName>
+    <definedName name="solver_lhs2" localSheetId="3" hidden="1">Mix!$B$5:$B$7</definedName>
+    <definedName name="solver_lhs3" localSheetId="3" hidden="1">Mix!$B$6</definedName>
+    <definedName name="solver_lhs4" localSheetId="3" hidden="1">Mix!$B$7</definedName>
+    <definedName name="solver_lhs5" localSheetId="3" hidden="1">Mix!$B$8</definedName>
+    <definedName name="solver_lhs6" localSheetId="3" hidden="1">Mix!$B$17</definedName>
+    <definedName name="solver_lhs7" localSheetId="3" hidden="1">Mix!$B$5</definedName>
+    <definedName name="solver_lhs8" localSheetId="3" hidden="1">Mix!$B$7</definedName>
+    <definedName name="solver_lhs9" localSheetId="3" hidden="1">Mix!$B$8</definedName>
+    <definedName name="solver_lin" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">7</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">Mix!$B$35</definedName>
+    <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="3" hidden="1">4</definedName>
+    <definedName name="solver_rel10" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rel11" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="3" hidden="1">3</definedName>
+    <definedName name="solver_rel3" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rel5" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rel6" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rel7" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rel8" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rel9" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="3" hidden="1">"integer"</definedName>
+    <definedName name="solver_rhs10" localSheetId="3" hidden="1">labor_rate_blended</definedName>
+    <definedName name="solver_rhs11" localSheetId="3" hidden="1">tomato_crop_cap</definedName>
+    <definedName name="solver_rhs2" localSheetId="3" hidden="1">0</definedName>
+    <definedName name="solver_rhs3" localSheetId="3" hidden="1">20</definedName>
+    <definedName name="solver_rhs4" localSheetId="3" hidden="1">30</definedName>
+    <definedName name="solver_rhs5" localSheetId="3" hidden="1">64</definedName>
+    <definedName name="solver_rhs6" localSheetId="3" hidden="1">4</definedName>
+    <definedName name="solver_rhs7" localSheetId="3" hidden="1">20</definedName>
+    <definedName name="solver_rhs8" localSheetId="3" hidden="1">mesclun_crop_cap</definedName>
+    <definedName name="solver_rhs9" localSheetId="3" hidden="1">carrot_crop_beds</definedName>
+    <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="3" hidden="1">2</definedName>
     <definedName name="temp_hrs_avail">Inputs!$B$20</definedName>
     <definedName name="temp_hrs_each">Inputs!$B$17</definedName>
     <definedName name="temp_hrs_used">Mix!$B$16</definedName>
@@ -124,7 +183,8 @@
     <definedName name="tomato_sched_temp">'MC Schedules'!$F$6:$F$26</definedName>
     <definedName name="tomato_sched_vc">'MC Schedules'!$I$6:$I$26</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -148,7 +208,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -6346,7 +6406,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" ref="A6:A26" si="0">ROW()-ROW(tomato_sched_anchor)</f>
         <v>0</v>
       </c>
       <c r="B6" s="16" t="str" cm="1">
@@ -6354,43 +6414,43 @@
         <v/>
       </c>
       <c r="C6" s="16" t="str">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" ref="C6:C26" si="1">IF(tomato_sched_q=0,"",tomato_crop_price)</f>
         <v/>
       </c>
       <c r="D6" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" ref="D6:D26" si="2">tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
         <v>0</v>
       </c>
       <c r="E6" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" ref="E6:E26" si="3">MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" ref="F6:F26" si="4">tomato_sched_hrs-tomato_sched_perm</f>
         <v>0</v>
       </c>
       <c r="G6" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" ref="G6:G26" si="5">tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
         <v>0</v>
       </c>
       <c r="H6" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" ref="H6:H26" si="6">tomato_sched_q*tomato_crop_fert</f>
         <v>0</v>
       </c>
       <c r="I6" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" ref="I6:I26" si="7">tomato_sched_labor+tomato_sched_fert</f>
         <v>0</v>
       </c>
       <c r="J6" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" ref="J6:J26" si="8">tomato_sched_vc+fixed_costs</f>
         <v>20000</v>
       </c>
       <c r="K6" s="16" t="str">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" ref="K6:K26" si="9">IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
         <v/>
       </c>
       <c r="L6" s="16" t="str">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" ref="L6:L26" si="10">IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
         <v/>
       </c>
       <c r="M6" s="20" t="str" cm="1">
@@ -6403,7 +6463,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="B7" s="16" cm="1">
@@ -6411,43 +6471,43 @@
         <v>4317.5</v>
       </c>
       <c r="C7" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D7" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>99.000000000000014</v>
       </c>
       <c r="E7" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>99.000000000000014</v>
       </c>
       <c r="F7" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G7" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>3437.5000000000005</v>
       </c>
       <c r="H7" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>880</v>
       </c>
       <c r="I7" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>4317.5</v>
       </c>
       <c r="J7" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>24317.5</v>
       </c>
       <c r="K7" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>4317.5</v>
       </c>
       <c r="L7" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>24317.5</v>
       </c>
       <c r="M7" s="20" t="str" cm="1">
@@ -6457,7 +6517,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B8" s="16" cm="1">
@@ -6465,43 +6525,43 @@
         <v>5005</v>
       </c>
       <c r="C8" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D8" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>217.80000000000004</v>
       </c>
       <c r="E8" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>217.80000000000004</v>
       </c>
       <c r="F8" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G8" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>7562.5000000000009</v>
       </c>
       <c r="H8" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>1760</v>
       </c>
       <c r="I8" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>9322.5</v>
       </c>
       <c r="J8" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>29322.5</v>
       </c>
       <c r="K8" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>4661.25</v>
       </c>
       <c r="L8" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>14661.25</v>
       </c>
       <c r="M8" s="20" t="str" cm="1">
@@ -6511,7 +6571,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B9" s="16" cm="1">
@@ -6519,43 +6579,43 @@
         <v>5795.6250000000036</v>
       </c>
       <c r="C9" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D9" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>359.37000000000012</v>
       </c>
       <c r="E9" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>359.37000000000012</v>
       </c>
       <c r="F9" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G9" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>12478.125000000004</v>
       </c>
       <c r="H9" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>2640</v>
       </c>
       <c r="I9" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>15118.125000000004</v>
       </c>
       <c r="J9" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>35118.125</v>
       </c>
       <c r="K9" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>5039.3750000000009</v>
       </c>
       <c r="L9" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>11706.041666666666</v>
       </c>
       <c r="M9" s="20" t="str" cm="1">
@@ -6565,7 +6625,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B10" s="16" cm="1">
@@ -6573,43 +6633,43 @@
         <v>6703.125</v>
       </c>
       <c r="C10" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D10" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>527.07600000000014</v>
       </c>
       <c r="E10" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>527.07600000000014</v>
       </c>
       <c r="F10" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G10" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>18301.250000000004</v>
       </c>
       <c r="H10" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>3520</v>
       </c>
       <c r="I10" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>21821.250000000004</v>
       </c>
       <c r="J10" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>41821.25</v>
       </c>
       <c r="K10" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>5455.3125000000009</v>
       </c>
       <c r="L10" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>10455.3125</v>
       </c>
       <c r="M10" s="20" t="str" cm="1">
@@ -6619,7 +6679,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B11" s="16" cm="1">
@@ -6627,43 +6687,43 @@
         <v>7660.859375</v>
       </c>
       <c r="C11" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D11" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>724.72950000000026</v>
       </c>
       <c r="E11" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F11" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>4.7295000000002574</v>
       </c>
       <c r="G11" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>25082.109375000004</v>
       </c>
       <c r="H11" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>4400</v>
       </c>
       <c r="I11" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>29482.109375000004</v>
       </c>
       <c r="J11" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>49482.109375</v>
       </c>
       <c r="K11" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>5896.4218750000009</v>
       </c>
       <c r="L11" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>9896.421875</v>
       </c>
       <c r="M11" s="20" t="str" cm="1">
@@ -6673,7 +6733,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B12" s="16" cm="1">
@@ -6681,43 +6741,43 @@
         <v>4906.2750000000051</v>
       </c>
       <c r="C12" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D12" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>956.64294000000041</v>
       </c>
       <c r="E12" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F12" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>236.64294000000041</v>
       </c>
       <c r="G12" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>29108.384375000009</v>
       </c>
       <c r="H12" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>5280</v>
       </c>
       <c r="I12" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>34388.384375000009</v>
       </c>
       <c r="J12" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>54388.384375000009</v>
       </c>
       <c r="K12" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>5731.3973958333345</v>
       </c>
       <c r="L12" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>9064.7307291666675</v>
       </c>
       <c r="M12" s="20" t="str" cm="1">
@@ -6727,7 +6787,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B13" s="16" cm="1">
@@ -6735,43 +6795,43 @@
         <v>5585.7089062500017</v>
       </c>
       <c r="C13" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D13" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>1227.6917730000007</v>
       </c>
       <c r="E13" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F13" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>507.69177300000069</v>
       </c>
       <c r="G13" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>33814.09328125001</v>
       </c>
       <c r="H13" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>6160</v>
       </c>
       <c r="I13" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>39974.09328125001</v>
       </c>
       <c r="J13" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>59974.09328125001</v>
       </c>
       <c r="K13" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>5710.5847544642875</v>
       </c>
       <c r="L13" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>8567.7276116071444</v>
       </c>
       <c r="M13" s="20" t="str" cm="1">
@@ -6781,7 +6841,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B14" s="16" cm="1">
@@ -6789,43 +6849,43 @@
         <v>6360.7668437500033</v>
       </c>
       <c r="C14" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D14" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>1543.3839432000009</v>
       </c>
       <c r="E14" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F14" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>823.38394320000089</v>
       </c>
       <c r="G14" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>39294.860125000014</v>
       </c>
       <c r="H14" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>7040</v>
       </c>
       <c r="I14" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>46334.860125000014</v>
       </c>
       <c r="J14" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>66334.860125000007</v>
       </c>
       <c r="K14" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>5791.8575156250017</v>
       </c>
       <c r="L14" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>8291.8575156250008</v>
       </c>
       <c r="M14" s="20" t="str" cm="1">
@@ -6835,7 +6895,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B15" s="16" cm="1">
@@ -6843,43 +6903,43 @@
         <v>7243.7792796875074</v>
       </c>
       <c r="C15" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D15" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>1909.9376297100011</v>
       </c>
       <c r="E15" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F15" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>1189.9376297100011</v>
       </c>
       <c r="G15" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>45658.639404687521</v>
       </c>
       <c r="H15" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>7920</v>
       </c>
       <c r="I15" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>53578.639404687521</v>
       </c>
       <c r="J15" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>73578.639404687521</v>
       </c>
       <c r="K15" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>5953.182156076391</v>
       </c>
       <c r="L15" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>8175.4043782986137</v>
       </c>
       <c r="M15" s="20" t="str" cm="1">
@@ -6889,7 +6949,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B16" s="16" cm="1">
@@ -6897,43 +6957,43 @@
         <v>8248.586534375012</v>
       </c>
       <c r="C16" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D16" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>2334.3682140900019</v>
       </c>
       <c r="E16" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F16" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>1614.3682140900019</v>
       </c>
       <c r="G16" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>53027.225939062533</v>
       </c>
       <c r="H16" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>8800</v>
       </c>
       <c r="I16" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>61827.225939062533</v>
       </c>
       <c r="J16" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>81827.22593906254</v>
       </c>
       <c r="K16" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>6182.7225939062537</v>
       </c>
       <c r="L16" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>8182.7225939062537</v>
       </c>
       <c r="M16" s="20" t="str" cm="1">
@@ -6943,7 +7003,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B17" s="16" cm="1">
@@ -6951,43 +7011,43 @@
         <v>9390.7174472031256</v>
       </c>
       <c r="C17" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D17" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>2824.5855390489023</v>
       </c>
       <c r="E17" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F17" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>2104.5855390489023</v>
       </c>
       <c r="G17" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>61537.943386265666</v>
       </c>
       <c r="H17" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>9680</v>
       </c>
       <c r="I17" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>71217.943386265659</v>
       </c>
       <c r="J17" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>91217.943386265659</v>
       </c>
       <c r="K17" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>6474.3584896605144</v>
       </c>
       <c r="L17" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>8292.5403078423333</v>
       </c>
       <c r="M17" s="20" t="str" cm="1">
@@ -6997,7 +7057,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B18" s="16" cm="1">
@@ -7005,43 +7065,43 @@
         <v>10687.588677253138</v>
       </c>
       <c r="C18" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D18" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>3389.502646858683</v>
       </c>
       <c r="E18" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F18" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>2669.502646858683</v>
       </c>
       <c r="G18" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>71345.532063518796</v>
       </c>
       <c r="H18" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>10560</v>
       </c>
       <c r="I18" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>81905.532063518796</v>
       </c>
       <c r="J18" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>101905.5320635188</v>
       </c>
       <c r="K18" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>6825.461005293233</v>
       </c>
       <c r="L18" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>8492.1276719598991</v>
       </c>
       <c r="M18" s="20" t="str" cm="1">
@@ -7051,7 +7111,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B19" s="16" cm="1">
@@ -7059,43 +7119,43 @@
         <v>12158.726978841107</v>
       </c>
       <c r="C19" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D19" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>4039.1573208399304</v>
       </c>
       <c r="E19" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F19" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>3319.1573208399304</v>
       </c>
       <c r="G19" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>82624.259042359903</v>
       </c>
       <c r="H19" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>11440</v>
       </c>
       <c r="I19" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>94064.259042359903</v>
       </c>
       <c r="J19" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>114064.2590423599</v>
       </c>
       <c r="K19" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>7235.7122340276846</v>
       </c>
       <c r="L19" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>8774.1737724892228</v>
       </c>
       <c r="M19" s="20" t="str" cm="1">
@@ -7105,7 +7165,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B20" s="16" cm="1">
@@ -7113,43 +7173,43 @@
         <v>13826.017053974152</v>
       </c>
       <c r="C20" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D20" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>4784.8479031488414</v>
       </c>
       <c r="E20" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F20" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>4064.8479031488414</v>
       </c>
       <c r="G20" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>95570.276096334055</v>
       </c>
       <c r="H20" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>12320</v>
       </c>
       <c r="I20" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>107890.27609633406</v>
       </c>
       <c r="J20" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>127890.27609633406</v>
       </c>
       <c r="K20" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>7706.4482925952898</v>
       </c>
       <c r="L20" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>9135.0197211667182</v>
       </c>
       <c r="M20" s="20" t="str" cm="1">
@@ -7159,7 +7219,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B21" s="16" cm="1">
@@ -7167,43 +7227,43 @@
         <v>15713.977874345364</v>
       </c>
       <c r="C21" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D21" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>5639.2850287111351</v>
       </c>
       <c r="E21" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F21" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>4919.2850287111351</v>
       </c>
       <c r="G21" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>110404.25397067942</v>
       </c>
       <c r="H21" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>13200</v>
       </c>
       <c r="I21" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>123604.25397067942</v>
       </c>
       <c r="J21" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>143604.25397067942</v>
       </c>
       <c r="K21" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>8240.2835980452946</v>
       </c>
       <c r="L21" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>9573.6169313786286</v>
       </c>
       <c r="M21" s="20" t="str" cm="1">
@@ -7213,7 +7273,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B22" s="16" cm="1">
@@ -7221,43 +7281,43 @@
         <v>17850.070688251115</v>
       </c>
       <c r="C22" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D22" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>6616.761100354398</v>
       </c>
       <c r="E22" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F22" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>5896.761100354398</v>
       </c>
       <c r="G22" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>127374.32465893052</v>
       </c>
       <c r="H22" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>14080</v>
       </c>
       <c r="I22" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>141454.32465893053</v>
       </c>
       <c r="J22" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>161454.32465893053</v>
       </c>
       <c r="K22" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>8840.8952911831584</v>
       </c>
       <c r="L22" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>10090.895291183158</v>
       </c>
       <c r="M22" s="20" t="str" cm="1">
@@ -7267,7 +7327,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B23" s="16" cm="1">
@@ -7275,43 +7335,43 @@
         <v>20265.042286194512</v>
       </c>
       <c r="C23" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D23" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>7733.3395360392033</v>
       </c>
       <c r="E23" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F23" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>7013.3395360392033</v>
       </c>
       <c r="G23" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>146759.36694512505</v>
       </c>
       <c r="H23" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>14960</v>
       </c>
       <c r="I23" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>161719.36694512505</v>
       </c>
       <c r="J23" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>181719.36694512505</v>
       </c>
       <c r="K23" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>9512.903937948533</v>
       </c>
       <c r="L23" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>10689.374526183827</v>
       </c>
       <c r="M23" s="20" t="str" cm="1">
@@ -7321,7 +7381,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B24" s="16" cm="1">
@@ -7329,43 +7389,43 @@
         <v>22993.307496844121</v>
       </c>
       <c r="C24" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D24" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>9007.0660478574246</v>
       </c>
       <c r="E24" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F24" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>8287.0660478574246</v>
       </c>
       <c r="G24" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>168872.67444196917</v>
       </c>
       <c r="H24" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>15840</v>
       </c>
       <c r="I24" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>184712.67444196917</v>
       </c>
       <c r="J24" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>204712.67444196917</v>
       </c>
       <c r="K24" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>10261.815246776065</v>
       </c>
       <c r="L24" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>11372.926357887176</v>
       </c>
       <c r="M24" s="20" t="str" cm="1">
@@ -7375,7 +7435,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B25" s="16" cm="1">
@@ -7383,43 +7443,43 @@
         <v>26073.375326761772</v>
       </c>
       <c r="C25" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D25" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>10458.204466678902</v>
       </c>
       <c r="E25" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F25" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>9738.2044666789025</v>
       </c>
       <c r="G25" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>194066.04976873094</v>
       </c>
       <c r="H25" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>16720</v>
       </c>
       <c r="I25" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>210786.04976873094</v>
       </c>
       <c r="J25" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>230786.04976873094</v>
       </c>
       <c r="K25" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>11094.002619406892</v>
       </c>
       <c r="L25" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>12146.634198354261</v>
       </c>
       <c r="M25" s="20" t="str" cm="1">
@@ -7429,7 +7489,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="19">
-        <f>ROW()-ROW(tomato_sched_anchor)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B26" s="16" cm="1">
@@ -7437,43 +7497,43 @@
         <v>29548.323647694342</v>
       </c>
       <c r="C26" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_crop_price)</f>
+        <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="D26" s="10">
-        <f>tomato_sched_q*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_sched_q</f>
+        <f t="shared" si="2"/>
         <v>12109.499908786096</v>
       </c>
       <c r="E26" s="10">
-        <f>MIN(_xlfn.SINGLE(tomato_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="F26" s="10">
-        <f>tomato_sched_hrs-tomato_sched_perm</f>
+        <f t="shared" si="4"/>
         <v>11389.499908786096</v>
       </c>
       <c r="G26" s="16">
-        <f>tomato_sched_perm*farmer_wage+tomato_sched_temp*temp_wage</f>
+        <f t="shared" si="5"/>
         <v>222734.37341642528</v>
       </c>
       <c r="H26" s="16">
-        <f>tomato_sched_q*tomato_crop_fert</f>
+        <f t="shared" si="6"/>
         <v>17600</v>
       </c>
       <c r="I26" s="16">
-        <f>tomato_sched_labor+tomato_sched_fert</f>
+        <f t="shared" si="7"/>
         <v>240334.37341642528</v>
       </c>
       <c r="J26" s="16">
-        <f>tomato_sched_vc+fixed_costs</f>
+        <f t="shared" si="8"/>
         <v>260334.37341642528</v>
       </c>
       <c r="K26" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_vc/tomato_sched_q)</f>
+        <f t="shared" si="9"/>
         <v>12016.718670821265</v>
       </c>
       <c r="L26" s="16">
-        <f>IF(tomato_sched_q=0,"",tomato_sched_tc/tomato_sched_q)</f>
+        <f t="shared" si="10"/>
         <v>13016.718670821265</v>
       </c>
       <c r="M26" s="20" t="str" cm="1">
@@ -7541,7 +7601,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" ref="A30:A50" si="11">ROW()-ROW(carrot_sched_anchor)</f>
         <v>0</v>
       </c>
       <c r="B30" s="16" t="str" cm="1">
@@ -7549,43 +7609,43 @@
         <v/>
       </c>
       <c r="C30" s="16" t="str">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" ref="C30:C50" si="12">IF(carrot_sched_q=0,"",carrot_crop_price)</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" ref="D30:D50" si="13">carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
         <v>0</v>
       </c>
       <c r="E30" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" ref="E30:E50" si="14">MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
         <v>0</v>
       </c>
       <c r="F30" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" ref="F30:F50" si="15">carrot_sched_hrs-carrot_sched_perm</f>
         <v>0</v>
       </c>
       <c r="G30" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" ref="G30:G50" si="16">carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
         <v>0</v>
       </c>
       <c r="H30" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" ref="H30:H50" si="17">carrot_sched_q*carrot_crop_fert</f>
         <v>0</v>
       </c>
       <c r="I30" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" ref="I30:I50" si="18">carrot_sched_labor+carrot_sched_fert</f>
         <v>0</v>
       </c>
       <c r="J30" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" ref="J30:J50" si="19">carrot_sched_vc+fixed_costs</f>
         <v>20000</v>
       </c>
       <c r="K30" s="16" t="str">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" ref="K30:K50" si="20">IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
         <v/>
       </c>
       <c r="L30" s="16" t="str">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" ref="L30:L50" si="21">IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
         <v/>
       </c>
       <c r="M30" s="20" t="str" cm="1">
@@ -7598,7 +7658,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="B31" s="16" cm="1">
@@ -7606,43 +7666,43 @@
         <v>1507.7083333333333</v>
       </c>
       <c r="C31" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D31" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>30.749999999999996</v>
       </c>
       <c r="E31" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>30.749999999999996</v>
       </c>
       <c r="F31" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G31" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>1067.7083333333333</v>
       </c>
       <c r="H31" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>440</v>
       </c>
       <c r="I31" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>1507.7083333333333</v>
       </c>
       <c r="J31" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>21507.708333333332</v>
       </c>
       <c r="K31" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1507.7083333333333</v>
       </c>
       <c r="L31" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>21507.708333333332</v>
       </c>
       <c r="M31" s="20" t="str" cm="1">
@@ -7652,7 +7712,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="B32" s="16" cm="1">
@@ -7660,43 +7720,43 @@
         <v>1561.0937499999998</v>
       </c>
       <c r="C32" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D32" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>63.037499999999994</v>
       </c>
       <c r="E32" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>63.037499999999994</v>
       </c>
       <c r="F32" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G32" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>2188.802083333333</v>
       </c>
       <c r="H32" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>880</v>
       </c>
       <c r="I32" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>3068.802083333333</v>
       </c>
       <c r="J32" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>23068.802083333332</v>
       </c>
       <c r="K32" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1534.4010416666665</v>
       </c>
       <c r="L32" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>11534.401041666666</v>
       </c>
       <c r="M32" s="20" t="str" cm="1">
@@ -7706,7 +7766,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="B33" s="16" cm="1">
@@ -7714,43 +7774,43 @@
         <v>1616.481119791667</v>
       </c>
       <c r="C33" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D33" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>96.920156249999991</v>
       </c>
       <c r="E33" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>96.920156249999991</v>
       </c>
       <c r="F33" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G33" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>3365.2832031249995</v>
       </c>
       <c r="H33" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>1320</v>
       </c>
       <c r="I33" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>4685.283203125</v>
       </c>
       <c r="J33" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>24685.283203125</v>
       </c>
       <c r="K33" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1561.7610677083333</v>
       </c>
       <c r="L33" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>8228.427734375</v>
       </c>
       <c r="M33" s="20" t="str" cm="1">
@@ -7760,7 +7820,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="B34" s="16" cm="1">
@@ -7768,43 +7828,43 @@
         <v>1673.9371744791652</v>
       </c>
       <c r="C34" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D34" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>132.45754687499996</v>
       </c>
       <c r="E34" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>132.45754687499996</v>
       </c>
       <c r="F34" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G34" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>4599.2203776041652</v>
       </c>
       <c r="H34" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>1760</v>
       </c>
       <c r="I34" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>6359.2203776041652</v>
       </c>
       <c r="J34" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>26359.220377604164</v>
       </c>
       <c r="K34" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1589.8050944010413</v>
       </c>
       <c r="L34" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>6589.8050944010411</v>
       </c>
       <c r="M34" s="20" t="str" cm="1">
@@ -7814,7 +7874,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="B35" s="16" cm="1">
@@ -7822,43 +7882,43 @@
         <v>1733.530731201171</v>
       </c>
       <c r="C35" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D35" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>169.71123193359369</v>
       </c>
       <c r="E35" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>169.71123193359369</v>
       </c>
       <c r="F35" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G35" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>5892.7511088053361</v>
       </c>
       <c r="H35" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>2200</v>
       </c>
       <c r="I35" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>8092.7511088053361</v>
       </c>
       <c r="J35" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>28092.751108805336</v>
       </c>
       <c r="K35" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1618.5502217610672</v>
       </c>
       <c r="L35" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>5618.5502217610674</v>
       </c>
       <c r="M35" s="20" t="str" cm="1">
@@ -7868,7 +7928,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="B36" s="16" cm="1">
@@ -7876,43 +7936,43 @@
         <v>1795.332755025227</v>
       </c>
       <c r="C36" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D36" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>208.74481527832023</v>
       </c>
       <c r="E36" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>208.74481527832023</v>
       </c>
       <c r="F36" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G36" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>7248.0838638305631</v>
       </c>
       <c r="H36" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>2640</v>
       </c>
       <c r="I36" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>9888.0838638305631</v>
       </c>
       <c r="J36" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>29888.083863830565</v>
       </c>
       <c r="K36" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1648.0139773050939</v>
       </c>
       <c r="L36" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>4981.3473106384272</v>
       </c>
       <c r="M36" s="20" t="str" cm="1">
@@ -7922,7 +7982,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="B37" s="16" cm="1">
@@ -7930,43 +7990,43 @@
         <v>1859.4164233334868</v>
       </c>
       <c r="C37" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D37" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>249.62400827032465</v>
       </c>
       <c r="E37" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>249.62400827032465</v>
       </c>
       <c r="F37" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G37" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>8667.50028716405</v>
       </c>
       <c r="H37" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>3080</v>
       </c>
       <c r="I37" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>11747.50028716405</v>
       </c>
       <c r="J37" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>31747.50028716405</v>
       </c>
       <c r="K37" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1678.2143267377214</v>
       </c>
       <c r="L37" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>4535.3571838805783</v>
       </c>
       <c r="M37" s="20" t="str" cm="1">
@@ -7976,7 +8036,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="B38" s="16" cm="1">
@@ -7984,43 +8044,43 @@
         <v>1925.8571920852646</v>
       </c>
       <c r="C38" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D38" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>292.41669540238024</v>
       </c>
       <c r="E38" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>292.41669540238024</v>
       </c>
       <c r="F38" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G38" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>10153.357479249315</v>
       </c>
       <c r="H38" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>3520</v>
       </c>
       <c r="I38" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>13673.357479249315</v>
       </c>
       <c r="J38" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>33673.357479249316</v>
       </c>
       <c r="K38" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1709.1696849061643</v>
       </c>
       <c r="L38" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>4209.1696849061645</v>
       </c>
       <c r="M38" s="20" t="str" cm="1">
@@ -8030,7 +8090,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="B39" s="16" cm="1">
@@ -8038,43 +8098,43 @@
         <v>1994.7328640100477</v>
       </c>
       <c r="C39" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D39" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>337.19300188586965</v>
       </c>
       <c r="E39" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>337.19300188586965</v>
       </c>
       <c r="F39" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G39" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>11708.090343259362</v>
       </c>
       <c r="H39" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>3960</v>
       </c>
       <c r="I39" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>15668.090343259362</v>
       </c>
       <c r="J39" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>35668.090343259362</v>
       </c>
       <c r="K39" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1740.898927028818</v>
       </c>
       <c r="L39" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>3963.1211492510402</v>
       </c>
       <c r="M39" s="20" t="str" cm="1">
@@ -8084,7 +8144,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="B40" s="16" cm="1">
@@ -8092,43 +8152,43 @@
         <v>2066.1236587860258</v>
       </c>
       <c r="C40" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D40" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>384.02536325890713</v>
       </c>
       <c r="E40" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>384.02536325890713</v>
       </c>
       <c r="F40" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G40" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>13334.214002045386</v>
       </c>
       <c r="H40" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>4400</v>
       </c>
       <c r="I40" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>17734.214002045388</v>
       </c>
       <c r="J40" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>37734.214002045388</v>
       </c>
       <c r="K40" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1773.4214002045387</v>
       </c>
       <c r="L40" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>3773.4214002045387</v>
       </c>
       <c r="M40" s="20" t="str" cm="1">
@@ -8138,7 +8198,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="B41" s="16" cm="1">
@@ -8146,43 +8206,43 @@
         <v>2140.1122852607878</v>
       </c>
       <c r="C41" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D41" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>432.98859707441784</v>
       </c>
       <c r="E41" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>432.98859707441784</v>
       </c>
       <c r="F41" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G41" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>15034.326287306174</v>
       </c>
       <c r="H41" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>4840</v>
       </c>
       <c r="I41" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>19874.326287306176</v>
       </c>
       <c r="J41" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>39874.326287306176</v>
       </c>
       <c r="K41" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1806.7569352096523</v>
       </c>
       <c r="L41" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>3624.9387533914705</v>
       </c>
       <c r="M41" s="20" t="str" cm="1">
@@ -8192,7 +8252,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="B42" s="16" cm="1">
@@ -8200,43 +8260,43 @@
         <v>2216.7840157725441</v>
       </c>
       <c r="C42" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D42" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>484.15997672866712</v>
       </c>
       <c r="E42" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>484.15997672866712</v>
       </c>
       <c r="F42" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G42" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>16811.11030307872</v>
       </c>
       <c r="H42" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>5280</v>
       </c>
       <c r="I42" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>22091.11030307872</v>
       </c>
       <c r="J42" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>42091.11030307872</v>
       </c>
       <c r="K42" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1840.9258585898933</v>
       </c>
       <c r="L42" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>3507.5925252565598</v>
       </c>
       <c r="M42" s="20" t="str" cm="1">
@@ -8246,7 +8306,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
       <c r="B43" s="16" cm="1">
@@ -8254,43 +8314,43 @@
         <v>2296.2267626316061</v>
       </c>
       <c r="C43" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D43" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>537.61930749245744</v>
       </c>
       <c r="E43" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>537.61930749245744</v>
       </c>
       <c r="F43" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G43" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>18667.337065710326</v>
       </c>
       <c r="H43" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>5720</v>
       </c>
       <c r="I43" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>24387.337065710326</v>
       </c>
       <c r="J43" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>44387.337065710322</v>
       </c>
       <c r="K43" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1875.9490050546406</v>
       </c>
       <c r="L43" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>3414.4105435161787</v>
       </c>
       <c r="M43" s="20" t="str" cm="1">
@@ -8300,7 +8360,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
       <c r="B44" s="16" cm="1">
@@ -8308,43 +8368,43 @@
         <v>2378.5311568237667</v>
       </c>
       <c r="C44" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D44" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>593.44900480898184</v>
       </c>
       <c r="E44" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>593.44900480898184</v>
       </c>
       <c r="F44" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G44" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>20605.868222534093</v>
       </c>
       <c r="H44" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>6160</v>
       </c>
       <c r="I44" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>26765.868222534093</v>
       </c>
       <c r="J44" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>46765.868222534089</v>
       </c>
       <c r="K44" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1911.8477301810067</v>
       </c>
       <c r="L44" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>3340.4191587524351</v>
       </c>
       <c r="M44" s="20" t="str" cm="1">
@@ -8354,7 +8414,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="B45" s="16" cm="1">
@@ -8362,43 +8422,43 @@
         <v>2463.7906289988823</v>
       </c>
       <c r="C45" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D45" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>651.73417492414967</v>
       </c>
       <c r="E45" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>651.73417492414967</v>
       </c>
       <c r="F45" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G45" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>22629.658851532975</v>
       </c>
       <c r="H45" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>6600</v>
       </c>
       <c r="I45" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>29229.658851532975</v>
       </c>
       <c r="J45" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>49229.658851532979</v>
       </c>
       <c r="K45" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1948.6439234355316</v>
       </c>
       <c r="L45" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>3281.9772567688651</v>
       </c>
       <c r="M45" s="20" t="str" cm="1">
@@ -8408,7 +8468,7 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>16</v>
       </c>
       <c r="B46" s="16" cm="1">
@@ -8416,43 +8476,43 @@
         <v>2552.1014928097429</v>
       </c>
       <c r="C46" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D46" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>712.5626979170703</v>
       </c>
       <c r="E46" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>712.5626979170703</v>
       </c>
       <c r="F46" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G46" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>24741.760344342718</v>
       </c>
       <c r="H46" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>7040</v>
       </c>
       <c r="I46" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>31781.760344342718</v>
       </c>
       <c r="J46" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>51781.760344342722</v>
       </c>
       <c r="K46" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1986.3600215214199</v>
       </c>
       <c r="L46" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>3236.3600215214201</v>
       </c>
       <c r="M46" s="20" t="str" cm="1">
@@ -8462,7 +8522,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>17</v>
       </c>
       <c r="B47" s="16" cm="1">
@@ -8470,43 +8530,43 @@
         <v>1670.9013431626554</v>
       </c>
       <c r="C47" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D47" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>776.02531320030937</v>
       </c>
       <c r="E47" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>720</v>
       </c>
       <c r="F47" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>56.02531320030937</v>
       </c>
       <c r="G47" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>25972.66168750537</v>
       </c>
       <c r="H47" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>7480</v>
       </c>
       <c r="I47" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>33452.661687505373</v>
       </c>
       <c r="J47" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>53452.661687505373</v>
       </c>
       <c r="K47" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1967.8036286767867</v>
       </c>
       <c r="L47" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>3144.2742169120806</v>
       </c>
       <c r="M47" s="20" t="str" cm="1">
@@ -8516,7 +8576,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>18</v>
       </c>
       <c r="B48" s="16" cm="1">
@@ -8524,43 +8584,43 @@
         <v>1589.1387909931072</v>
       </c>
       <c r="C48" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D48" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>842.2157075615122</v>
       </c>
       <c r="E48" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>720</v>
       </c>
       <c r="F48" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>122.2157075615122</v>
       </c>
       <c r="G48" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>27121.800478498477</v>
       </c>
       <c r="H48" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>7920</v>
       </c>
       <c r="I48" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>35041.800478498481</v>
       </c>
       <c r="J48" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>55041.800478498481</v>
       </c>
       <c r="K48" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1946.7666932499155</v>
       </c>
       <c r="L48" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>3057.8778043610268</v>
       </c>
       <c r="M48" s="20" t="str" cm="1">
@@ -8570,7 +8630,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>19</v>
       </c>
       <c r="B49" s="16" cm="1">
@@ -8578,43 +8638,43 @@
         <v>1638.1753169880685</v>
       </c>
       <c r="C49" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D49" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>911.23060582002495</v>
       </c>
       <c r="E49" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>720</v>
       </c>
       <c r="F49" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>191.23060582002495</v>
       </c>
       <c r="G49" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>28319.975795486545</v>
       </c>
       <c r="H49" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>8360</v>
       </c>
       <c r="I49" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>36679.975795486549</v>
       </c>
       <c r="J49" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>56679.975795486549</v>
       </c>
       <c r="K49" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1930.5250418677131</v>
       </c>
       <c r="L49" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>2983.1566208150816</v>
       </c>
       <c r="M49" s="20" t="str" cm="1">
@@ -8624,7 +8684,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="19">
-        <f>ROW()-ROW(carrot_sched_anchor)</f>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="B50" s="16" cm="1">
@@ -8632,43 +8692,43 @@
         <v>1688.9454575384007</v>
       </c>
       <c r="C50" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_crop_price)</f>
+        <f t="shared" si="12"/>
         <v>2094</v>
       </c>
       <c r="D50" s="10">
-        <f>carrot_sched_q*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_sched_q</f>
+        <f t="shared" si="13"/>
         <v>983.16986417423732</v>
       </c>
       <c r="E50" s="10">
-        <f>MIN(_xlfn.SINGLE(carrot_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="14"/>
         <v>720</v>
       </c>
       <c r="F50" s="10">
-        <f>carrot_sched_hrs-carrot_sched_perm</f>
+        <f t="shared" si="15"/>
         <v>263.16986417423732</v>
       </c>
       <c r="G50" s="16">
-        <f>carrot_sched_perm*farmer_wage+carrot_sched_temp*temp_wage</f>
+        <f t="shared" si="16"/>
         <v>29568.921253024953</v>
       </c>
       <c r="H50" s="16">
-        <f>carrot_sched_q*carrot_crop_fert</f>
+        <f t="shared" si="17"/>
         <v>8800</v>
       </c>
       <c r="I50" s="16">
-        <f>carrot_sched_labor+carrot_sched_fert</f>
+        <f t="shared" si="18"/>
         <v>38368.92125302495</v>
       </c>
       <c r="J50" s="16">
-        <f>carrot_sched_vc+fixed_costs</f>
+        <f t="shared" si="19"/>
         <v>58368.92125302495</v>
       </c>
       <c r="K50" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_vc/carrot_sched_q)</f>
+        <f t="shared" si="20"/>
         <v>1918.4460626512475</v>
       </c>
       <c r="L50" s="16">
-        <f>IF(carrot_sched_q=0,"",carrot_sched_tc/carrot_sched_q)</f>
+        <f t="shared" si="21"/>
         <v>2918.4460626512473</v>
       </c>
       <c r="M50" s="20" t="str" cm="1">
@@ -8736,7 +8796,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" ref="A54:A84" si="22">ROW()-ROW(mesclun_sched_anchor)</f>
         <v>0</v>
       </c>
       <c r="B54" s="16" t="str" cm="1">
@@ -8744,43 +8804,43 @@
         <v/>
       </c>
       <c r="C54" s="16" t="str">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" ref="C54:C84" si="23">IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
         <v/>
       </c>
       <c r="D54" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" ref="D54:D84" si="24">mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
         <v>0</v>
       </c>
       <c r="E54" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" ref="E54:E84" si="25">MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
         <v>0</v>
       </c>
       <c r="F54" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" ref="F54:F84" si="26">mesclun_sched_hrs-mesclun_sched_perm</f>
         <v>0</v>
       </c>
       <c r="G54" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" ref="G54:G84" si="27">mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
         <v>0</v>
       </c>
       <c r="H54" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" ref="H54:H84" si="28">mesclun_sched_q*mesclun_crop_fert</f>
         <v>0</v>
       </c>
       <c r="I54" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" ref="I54:I84" si="29">mesclun_sched_labor+mesclun_sched_fert</f>
         <v>0</v>
       </c>
       <c r="J54" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" ref="J54:J84" si="30">mesclun_sched_vc+fixed_costs</f>
         <v>20000</v>
       </c>
       <c r="K54" s="16" t="str">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" ref="K54:K84" si="31">IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
         <v/>
       </c>
       <c r="L54" s="16" t="str">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" ref="L54:L84" si="32">IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
         <v/>
       </c>
       <c r="M54" s="20" t="str" cm="1">
@@ -8793,7 +8853,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="B55" s="16" cm="1">
@@ -8801,43 +8861,43 @@
         <v>2462.03125</v>
       </c>
       <c r="C55" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D55" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>45.5625</v>
       </c>
       <c r="E55" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>45.5625</v>
       </c>
       <c r="F55" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G55" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>1582.03125</v>
       </c>
       <c r="H55" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>880</v>
       </c>
       <c r="I55" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>2462.03125</v>
       </c>
       <c r="J55" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>22462.03125</v>
       </c>
       <c r="K55" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2462.03125</v>
       </c>
       <c r="L55" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>22462.03125</v>
       </c>
       <c r="M55" s="20" t="str" cm="1">
@@ -8847,7 +8907,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
       <c r="B56" s="16" cm="1">
@@ -8855,43 +8915,43 @@
         <v>2501.58203125</v>
       </c>
       <c r="C56" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D56" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>92.264062499999994</v>
       </c>
       <c r="E56" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>92.264062499999994</v>
       </c>
       <c r="F56" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G56" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>3203.6132812499995</v>
       </c>
       <c r="H56" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>1760</v>
       </c>
       <c r="I56" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>4963.61328125</v>
       </c>
       <c r="J56" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>24963.61328125</v>
       </c>
       <c r="K56" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2481.806640625</v>
       </c>
       <c r="L56" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>12481.806640625</v>
       </c>
       <c r="M56" s="20" t="str" cm="1">
@@ -8901,7 +8961,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
       <c r="B57" s="16" cm="1">
@@ -8909,43 +8969,43 @@
         <v>2541.8743896484366</v>
       </c>
       <c r="C57" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D57" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>140.12604492187498</v>
       </c>
       <c r="E57" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>140.12604492187498</v>
       </c>
       <c r="F57" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G57" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>4865.4876708984366</v>
       </c>
       <c r="H57" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>2640</v>
       </c>
       <c r="I57" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>7505.4876708984366</v>
       </c>
       <c r="J57" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>27505.487670898438</v>
       </c>
       <c r="K57" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2501.829223632812</v>
       </c>
       <c r="L57" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>9168.4958902994786</v>
       </c>
       <c r="M57" s="20" t="str" cm="1">
@@ -8955,7 +9015,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>4</v>
       </c>
       <c r="B58" s="16" cm="1">
@@ -8963,43 +9023,43 @@
         <v>2582.920684814454</v>
       </c>
       <c r="C58" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D58" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>189.17016064453125</v>
       </c>
       <c r="E58" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>189.17016064453125</v>
       </c>
       <c r="F58" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G58" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>6568.4083557128906</v>
       </c>
       <c r="H58" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>3520</v>
       </c>
       <c r="I58" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>10088.408355712891</v>
       </c>
       <c r="J58" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>30088.408355712891</v>
       </c>
       <c r="K58" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2522.1020889282227</v>
       </c>
       <c r="L58" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>7522.1020889282227</v>
       </c>
       <c r="M58" s="20" t="str" cm="1">
@@ -9009,7 +9069,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="B59" s="16" cm="1">
@@ -9017,43 +9077,43 @@
         <v>2624.7334694862348</v>
       </c>
       <c r="C59" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D59" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>239.41848456573481</v>
       </c>
       <c r="E59" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>239.41848456573481</v>
       </c>
       <c r="F59" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G59" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>8313.1418251991254</v>
       </c>
       <c r="H59" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>4400</v>
       </c>
       <c r="I59" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>12713.141825199125</v>
       </c>
       <c r="J59" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>32713.141825199127</v>
       </c>
       <c r="K59" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2542.628365039825</v>
       </c>
       <c r="L59" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>6542.6283650398254</v>
       </c>
       <c r="M59" s="20" t="str" cm="1">
@@ -9063,7 +9123,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>6</v>
       </c>
       <c r="B60" s="16" cm="1">
@@ -9071,43 +9131,43 @@
         <v>2667.3254924178127</v>
       </c>
       <c r="C60" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D60" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>290.89345874736784</v>
       </c>
       <c r="E60" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>290.89345874736784</v>
       </c>
       <c r="F60" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G60" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>10100.467317616938</v>
       </c>
       <c r="H60" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>5280</v>
       </c>
       <c r="I60" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>15380.467317616938</v>
       </c>
       <c r="J60" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>35380.467317616938</v>
       </c>
       <c r="K60" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2563.4112196028232</v>
       </c>
       <c r="L60" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>5896.7445529361567</v>
       </c>
       <c r="M60" s="20" t="str" cm="1">
@@ -9117,7 +9177,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
       <c r="B61" s="16" cm="1">
@@ -9125,43 +9185,43 @@
         <v>2710.7097013180683</v>
       </c>
       <c r="C61" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D61" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>343.61789814532818</v>
       </c>
       <c r="E61" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>343.61789814532818</v>
       </c>
       <c r="F61" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G61" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>11931.177018935006</v>
       </c>
       <c r="H61" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>6160</v>
       </c>
       <c r="I61" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>18091.177018935006</v>
       </c>
       <c r="J61" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>38091.177018935006</v>
       </c>
       <c r="K61" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2584.453859847858</v>
       </c>
       <c r="L61" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>5441.5967169907153</v>
       </c>
       <c r="M61" s="20" t="str" cm="1">
@@ -9171,7 +9231,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>8</v>
       </c>
       <c r="B62" s="16" cm="1">
@@ -9179,43 +9239,43 @@
         <v>2754.8992458326466</v>
       </c>
       <c r="C62" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D62" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>397.61499642530839</v>
       </c>
       <c r="E62" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>397.61499642530839</v>
       </c>
       <c r="F62" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G62" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>13806.076264767653</v>
       </c>
       <c r="H62" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>7040</v>
       </c>
       <c r="I62" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>20846.076264767653</v>
       </c>
       <c r="J62" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>40846.076264767653</v>
       </c>
       <c r="K62" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2605.7595330959566</v>
       </c>
       <c r="L62" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>5105.7595330959566</v>
       </c>
       <c r="M62" s="20" t="str" cm="1">
@@ -9225,7 +9285,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
       <c r="B63" s="16" cm="1">
@@ -9233,43 +9293,43 @@
         <v>2799.9074805692508</v>
       </c>
       <c r="C63" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D63" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>452.90833186570285</v>
       </c>
       <c r="E63" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>452.90833186570285</v>
       </c>
       <c r="F63" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G63" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>15725.983745336904</v>
       </c>
       <c r="H63" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>7920</v>
       </c>
       <c r="I63" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>23645.983745336904</v>
       </c>
       <c r="J63" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>43645.983745336904</v>
       </c>
       <c r="K63" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2627.331527259656</v>
       </c>
       <c r="L63" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>4849.5537494818782</v>
       </c>
       <c r="M63" s="20" t="str" cm="1">
@@ -9279,7 +9339,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="B64" s="16" cm="1">
@@ -9287,43 +9347,43 @@
         <v>2845.7479681671139</v>
       </c>
       <c r="C64" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D64" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>509.52187334891573</v>
       </c>
       <c r="E64" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>509.52187334891573</v>
       </c>
       <c r="F64" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G64" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>17691.731713504018</v>
       </c>
       <c r="H64" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>8800</v>
       </c>
       <c r="I64" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>26491.731713504018</v>
       </c>
       <c r="J64" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>46491.731713504021</v>
       </c>
       <c r="K64" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2649.1731713504018</v>
       </c>
       <c r="L64" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>4649.1731713504023</v>
       </c>
       <c r="M64" s="20" t="str" cm="1">
@@ -9333,7 +9393,7 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>11</v>
       </c>
       <c r="B65" s="16" cm="1">
@@ -9341,43 +9401,43 @@
         <v>2892.4344824110776</v>
       </c>
       <c r="C65" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D65" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>567.47998644235474</v>
       </c>
       <c r="E65" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>567.47998644235474</v>
       </c>
       <c r="F65" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G65" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>19704.166195915095</v>
       </c>
       <c r="H65" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>9680</v>
       </c>
       <c r="I65" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>29384.166195915095</v>
       </c>
       <c r="J65" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>49384.166195915095</v>
       </c>
       <c r="K65" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2671.2878359922815</v>
       </c>
       <c r="L65" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>4489.4696541740996</v>
       </c>
       <c r="M65" s="20" t="str" cm="1">
@@ -9387,7 +9447,7 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>12</v>
       </c>
       <c r="B66" s="16" cm="1">
@@ -9395,43 +9455,43 @@
         <v>2939.9810113911262</v>
       </c>
       <c r="C66" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D66" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>626.80743957041921</v>
       </c>
       <c r="E66" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>626.80743957041921</v>
       </c>
       <c r="F66" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G66" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>21764.147207306221</v>
       </c>
       <c r="H66" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>10560</v>
       </c>
       <c r="I66" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>32324.147207306221</v>
       </c>
       <c r="J66" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>52324.147207306218</v>
       </c>
       <c r="K66" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2693.6789339421853</v>
       </c>
       <c r="L66" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>4360.3456006088518</v>
       </c>
       <c r="M66" s="20" t="str" cm="1">
@@ -9441,7 +9501,7 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>13</v>
       </c>
       <c r="B67" s="16" cm="1">
@@ -9449,43 +9509,43 @@
         <v>2988.4017607077876</v>
       </c>
       <c r="C67" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D67" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>687.52941027880343</v>
       </c>
       <c r="E67" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>687.52941027880343</v>
       </c>
       <c r="F67" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G67" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>23872.548968014009</v>
       </c>
       <c r="H67" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>11440</v>
       </c>
       <c r="I67" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>35312.548968014009</v>
       </c>
       <c r="J67" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>55312.548968014009</v>
       </c>
       <c r="K67" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2716.3499206164624</v>
       </c>
       <c r="L67" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>4254.8114590780006</v>
       </c>
       <c r="M67" s="20" t="str" cm="1">
@@ -9495,7 +9555,7 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>14</v>
       </c>
       <c r="B68" s="16" cm="1">
@@ -9503,43 +9563,43 @@
         <v>2522.5810943551696</v>
       </c>
       <c r="C68" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D68" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>749.67149159246469</v>
       </c>
       <c r="E68" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F68" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>29.67149159246469</v>
       </c>
       <c r="G68" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>25515.130062369179</v>
       </c>
       <c r="H68" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>12320</v>
       </c>
       <c r="I68" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>37835.130062369179</v>
       </c>
       <c r="J68" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>57835.130062369179</v>
       </c>
       <c r="K68" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2702.5092901692269</v>
       </c>
       <c r="L68" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>4131.0807187406554</v>
       </c>
       <c r="M68" s="20" t="str" cm="1">
@@ -9549,7 +9609,7 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>15</v>
       </c>
       <c r="B69" s="16" cm="1">
@@ -9557,43 +9617,43 @@
         <v>1983.9619249331008</v>
       </c>
       <c r="C69" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D69" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>813.25969846861108</v>
       </c>
       <c r="E69" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F69" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>93.259698468611077</v>
       </c>
       <c r="G69" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>26619.091987302276</v>
       </c>
       <c r="H69" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>13200</v>
       </c>
       <c r="I69" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>39819.091987302279</v>
       </c>
       <c r="J69" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>59819.091987302279</v>
       </c>
       <c r="K69" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2654.6061324868188</v>
       </c>
       <c r="L69" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3987.9394658201518</v>
       </c>
       <c r="M69" s="20" t="str" cm="1">
@@ -9603,7 +9663,7 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>16</v>
       </c>
       <c r="B70" s="16" cm="1">
@@ -9611,43 +9671,43 @@
         <v>2009.5273589841818</v>
       </c>
       <c r="C70" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D70" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>878.32047434610013</v>
       </c>
       <c r="E70" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F70" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>158.32047434610013</v>
       </c>
       <c r="G70" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>27748.619346286461</v>
       </c>
       <c r="H70" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>14080</v>
       </c>
       <c r="I70" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>41828.619346286461</v>
       </c>
       <c r="J70" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>61828.619346286461</v>
       </c>
       <c r="K70" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2614.2887091429038</v>
       </c>
       <c r="L70" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3864.2887091429038</v>
       </c>
       <c r="M70" s="20" t="str" cm="1">
@@ -9657,7 +9717,7 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>17</v>
       </c>
       <c r="B71" s="16" cm="1">
@@ -9665,43 +9725,43 @@
         <v>2035.5594348357699</v>
       </c>
       <c r="C71" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D71" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>944.88069779264049</v>
       </c>
       <c r="E71" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F71" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>224.88069779264049</v>
       </c>
       <c r="G71" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>28904.178781122231</v>
       </c>
       <c r="H71" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>14960</v>
       </c>
       <c r="I71" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>43864.178781122231</v>
       </c>
       <c r="J71" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>63864.178781122231</v>
       </c>
       <c r="K71" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2580.245810654249</v>
       </c>
       <c r="L71" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3756.7163988895431</v>
       </c>
       <c r="M71" s="20" t="str" cm="1">
@@ -9711,7 +9771,7 @@
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>18</v>
       </c>
       <c r="B72" s="16" cm="1">
@@ -9719,43 +9779,43 @@
         <v>2062.0658239338081</v>
       </c>
       <c r="C72" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D72" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1012.9676892512279</v>
       </c>
       <c r="E72" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F72" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>292.96768925122785</v>
       </c>
       <c r="G72" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>30086.244605056039</v>
       </c>
       <c r="H72" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>15840</v>
       </c>
       <c r="I72" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>45926.244605056039</v>
       </c>
       <c r="J72" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>65926.244605056039</v>
       </c>
       <c r="K72" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2551.4580336142244</v>
       </c>
       <c r="L72" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3662.5691447253357</v>
       </c>
       <c r="M72" s="20" t="str" cm="1">
@@ -9765,7 +9825,7 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>19</v>
       </c>
       <c r="B73" s="16" cm="1">
@@ -9773,43 +9833,43 @@
         <v>2089.0543165975978</v>
       </c>
       <c r="C73" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D73" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1082.6092178872495</v>
       </c>
       <c r="E73" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F73" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>362.60921788724954</v>
       </c>
       <c r="G73" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>31295.298921653637</v>
       </c>
       <c r="H73" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>16720</v>
       </c>
       <c r="I73" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>48015.298921653637</v>
       </c>
       <c r="J73" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>68015.298921653637</v>
       </c>
       <c r="K73" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2527.1209958765071</v>
       </c>
       <c r="L73" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3579.7525748238754</v>
       </c>
       <c r="M73" s="20" t="str" cm="1">
@@ -9819,7 +9879,7 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="B74" s="16" cm="1">
@@ -9827,43 +9887,43 @@
         <v>2116.532823793008</v>
       </c>
       <c r="C74" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D74" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1153.8335085377266</v>
       </c>
       <c r="E74" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F74" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>433.83350853772663</v>
       </c>
       <c r="G74" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>32531.831745446641</v>
       </c>
       <c r="H74" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>17600</v>
       </c>
       <c r="I74" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>50131.831745446645</v>
       </c>
       <c r="J74" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>70131.831745446645</v>
       </c>
       <c r="K74" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2506.5915872723322</v>
       </c>
       <c r="L74" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3506.5915872723322</v>
       </c>
       <c r="M74" s="20" t="str" cm="1">
@@ -9873,7 +9933,7 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>21</v>
       </c>
       <c r="B75" s="16" cm="1">
@@ -9881,43 +9941,43 @@
         <v>2144.5093789313105</v>
       </c>
       <c r="C75" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D75" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1226.6692487641703</v>
       </c>
       <c r="E75" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F75" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>506.66924876417033</v>
       </c>
       <c r="G75" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>33796.341124377956</v>
       </c>
       <c r="H75" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>18480</v>
       </c>
       <c r="I75" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>52276.341124377956</v>
       </c>
       <c r="J75" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>72276.341124377956</v>
       </c>
       <c r="K75" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2489.3495773513314</v>
       </c>
       <c r="L75" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3441.7305297322837</v>
       </c>
       <c r="M75" s="20" t="str" cm="1">
@@ -9927,7 +9987,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>22</v>
       </c>
       <c r="B76" s="16" cm="1">
@@ -9935,43 +9995,43 @@
         <v>2172.9921396943828</v>
       </c>
       <c r="C76" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D76" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1301.1455960105666</v>
       </c>
       <c r="E76" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F76" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>581.14559601056658</v>
       </c>
       <c r="G76" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>35089.333264072338</v>
       </c>
       <c r="H76" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>19360</v>
       </c>
       <c r="I76" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>54449.333264072338</v>
       </c>
       <c r="J76" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>74449.333264072338</v>
       </c>
       <c r="K76" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2474.9696938214697</v>
       </c>
       <c r="L76" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3384.0606029123792</v>
       </c>
       <c r="M76" s="20" t="str" cm="1">
@@ -9981,7 +10041,7 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>23</v>
       </c>
       <c r="B77" s="16" cm="1">
@@ -9989,43 +10049,43 @@
         <v>2201.9893898860464</v>
       </c>
       <c r="C77" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D77" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1377.292184868003</v>
       </c>
       <c r="E77" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F77" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>657.29218486800301</v>
       </c>
       <c r="G77" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>36411.322653958385</v>
       </c>
       <c r="H77" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>20240</v>
       </c>
       <c r="I77" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>56651.322653958385</v>
       </c>
       <c r="J77" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>76651.322653958385</v>
       </c>
       <c r="K77" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2463.1009849547122</v>
       </c>
       <c r="L77" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3332.6662023460167</v>
       </c>
       <c r="M77" s="20" t="str" cm="1">
@@ -10035,7 +10095,7 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>24</v>
       </c>
       <c r="B78" s="16" cm="1">
@@ -10043,43 +10103,43 @@
         <v>2231.5095413106901</v>
       </c>
       <c r="C78" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D78" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1455.1391344474989</v>
       </c>
       <c r="E78" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F78" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>735.13913444749892</v>
       </c>
       <c r="G78" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>37762.832195269075</v>
       </c>
       <c r="H78" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>21120</v>
       </c>
       <c r="I78" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>58882.832195269075</v>
       </c>
       <c r="J78" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>78882.832195269075</v>
       </c>
       <c r="K78" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2453.4513414695448</v>
       </c>
       <c r="L78" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3286.7846748028783</v>
       </c>
       <c r="M78" s="20" t="str" cm="1">
@@ -10089,7 +10149,7 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>25</v>
       </c>
       <c r="B79" s="16" cm="1">
@@ -10097,43 +10157,43 @@
         <v>2261.5611356787776</v>
       </c>
       <c r="C79" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D79" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1534.7170558625965</v>
       </c>
       <c r="E79" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F79" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>814.71705586259645</v>
       </c>
       <c r="G79" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>39144.393330947853</v>
       </c>
       <c r="H79" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>22000</v>
       </c>
       <c r="I79" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>61144.393330947853</v>
       </c>
       <c r="J79" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>81144.393330947845</v>
       </c>
       <c r="K79" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2445.7757332379142</v>
       </c>
       <c r="L79" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3245.7757332379138</v>
       </c>
       <c r="M79" s="20" t="str" cm="1">
@@ -10143,7 +10203,7 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>26</v>
       </c>
       <c r="B80" s="16" cm="1">
@@ -10151,43 +10211,43 @@
         <v>2292.1528465402444</v>
       </c>
       <c r="C80" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D80" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1616.0570598233144</v>
       </c>
       <c r="E80" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F80" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>896.05705982331438</v>
       </c>
       <c r="G80" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>40556.546177488097</v>
       </c>
       <c r="H80" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>22880</v>
       </c>
       <c r="I80" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>63436.546177488097</v>
       </c>
       <c r="J80" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>83436.546177488097</v>
       </c>
       <c r="K80" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2439.8671606726193</v>
       </c>
       <c r="L80" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3209.0979299033884</v>
       </c>
       <c r="M80" s="20" t="str" cm="1">
@@ -10197,7 +10257,7 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>27</v>
       </c>
       <c r="B81" s="16" cm="1">
@@ -10205,43 +10265,43 @@
         <v>2323.2934812457679</v>
       </c>
       <c r="C81" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D81" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1699.1907643430709</v>
       </c>
       <c r="E81" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F81" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>979.1907643430709</v>
       </c>
       <c r="G81" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>41999.839658733865</v>
       </c>
       <c r="H81" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>23760</v>
       </c>
       <c r="I81" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>65759.839658733865</v>
       </c>
       <c r="J81" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>85759.839658733865</v>
       </c>
       <c r="K81" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2435.549616990143</v>
       </c>
       <c r="L81" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3176.2903577308839</v>
       </c>
       <c r="M81" s="20" t="str" cm="1">
@@ -10251,7 +10311,7 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>28</v>
       </c>
       <c r="B82" s="16" cm="1">
@@ -10259,43 +10319,43 @@
         <v>2354.9919829366991</v>
       </c>
       <c r="C82" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D82" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1784.1503025602246</v>
       </c>
       <c r="E82" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F82" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>1064.1503025602246</v>
       </c>
       <c r="G82" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>43474.831641670564</v>
       </c>
       <c r="H82" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>24640</v>
       </c>
       <c r="I82" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>68114.831641670564</v>
       </c>
       <c r="J82" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>88114.831641670564</v>
       </c>
       <c r="K82" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2432.6725586310918</v>
       </c>
       <c r="L82" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3146.958272916806</v>
       </c>
       <c r="M82" s="20" t="str" cm="1">
@@ -10305,7 +10365,7 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="B83" s="16" cm="1">
@@ -10313,43 +10373,43 @@
         <v>2387.2574325634341</v>
       </c>
       <c r="C83" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D83" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1870.9683306758782</v>
       </c>
       <c r="E83" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F83" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>1150.9683306758782</v>
       </c>
       <c r="G83" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>44982.089074233998</v>
       </c>
       <c r="H83" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>25520</v>
       </c>
       <c r="I83" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>70502.089074233998</v>
       </c>
       <c r="J83" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>90502.089074233998</v>
       </c>
       <c r="K83" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2431.1065198011725</v>
       </c>
       <c r="L83" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3120.7616922149655</v>
       </c>
       <c r="M83" s="20" t="str" cm="1">
@@ -10359,7 +10419,7 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="19">
-        <f>ROW()-ROW(mesclun_sched_anchor)</f>
+        <f t="shared" si="22"/>
         <v>30</v>
       </c>
       <c r="B84" s="16" cm="1">
@@ -10367,43 +10427,43 @@
         <v>2420.0990509335097</v>
       </c>
       <c r="C84" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_crop_price)</f>
+        <f t="shared" si="23"/>
         <v>2700</v>
       </c>
       <c r="D84" s="10">
-        <f>mesclun_sched_q*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_sched_q</f>
+        <f t="shared" si="24"/>
         <v>1959.6780360096488</v>
       </c>
       <c r="E84" s="10">
-        <f>MIN(_xlfn.SINGLE(mesclun_sched_hrs),farmer_hrs_field)</f>
+        <f t="shared" si="25"/>
         <v>720</v>
       </c>
       <c r="F84" s="10">
-        <f>mesclun_sched_hrs-mesclun_sched_perm</f>
+        <f t="shared" si="26"/>
         <v>1239.6780360096488</v>
       </c>
       <c r="G84" s="16">
-        <f>mesclun_sched_perm*farmer_wage+mesclun_sched_temp*temp_wage</f>
+        <f t="shared" si="27"/>
         <v>46522.188125167515</v>
       </c>
       <c r="H84" s="16">
-        <f>mesclun_sched_q*mesclun_crop_fert</f>
+        <f t="shared" si="28"/>
         <v>26400</v>
       </c>
       <c r="I84" s="16">
-        <f>mesclun_sched_labor+mesclun_sched_fert</f>
+        <f t="shared" si="29"/>
         <v>72922.188125167508</v>
       </c>
       <c r="J84" s="16">
-        <f>mesclun_sched_vc+fixed_costs</f>
+        <f t="shared" si="30"/>
         <v>92922.188125167508</v>
       </c>
       <c r="K84" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_vc/mesclun_sched_q)</f>
+        <f t="shared" si="31"/>
         <v>2430.7396041722504</v>
       </c>
       <c r="L84" s="16">
-        <f>IF(mesclun_sched_q=0,"",mesclun_sched_tc/mesclun_sched_q)</f>
+        <f t="shared" si="32"/>
         <v>3097.406270838917</v>
       </c>
       <c r="M84" s="20" t="str" cm="1">
@@ -10577,12 +10637,12 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>89</v>
       </c>
       <c r="B5" s="25">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
         <v>90</v>
@@ -10611,7 +10671,7 @@
         <v>91</v>
       </c>
       <c r="B6" s="25">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>90</v>
@@ -10625,7 +10685,7 @@
       </c>
       <c r="I6" s="31">
         <f>mix_beds_total</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J6" s="32" t="str">
         <f>IF(mix_beds_total&gt;=beds_total-0.0001,"BINDING","SLACK")</f>
@@ -10635,14 +10695,16 @@
         <f>IF(mix_beds_total&lt;=beds_total+0.0001,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="33">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>92</v>
       </c>
       <c r="B7" s="25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>90</v>
@@ -10656,7 +10718,7 @@
       </c>
       <c r="I7" s="31">
         <f>tomato_crop_beds</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J7" s="32" t="str">
         <f>IF(tomato_crop_beds&gt;=tomato_crop_cap-0.0001,"BINDING","SLACK")</f>
@@ -10666,7 +10728,9 @@
         <f>IF(tomato_crop_beds&lt;=tomato_crop_cap+0.0001,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="L7" s="33"/>
+      <c r="L7" s="33">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -10674,7 +10738,7 @@
       </c>
       <c r="B8" s="24">
         <f>SUM(mix_beds_row)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
@@ -10688,17 +10752,19 @@
       </c>
       <c r="I8" s="31">
         <f>carrot_crop_beds</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J8" s="32" t="str">
         <f>IF(carrot_crop_beds&gt;=carrot_crop_cap-0.0001,"BINDING","SLACK")</f>
-        <v>SLACK</v>
+        <v>BINDING</v>
       </c>
       <c r="K8" s="32" t="str">
         <f>IF(carrot_crop_beds&lt;=carrot_crop_cap+0.0001,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="33">
+        <v>352.5</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G9" t="s">
@@ -10710,17 +10776,19 @@
       </c>
       <c r="I9" s="31">
         <f>mesclun_crop_beds</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J9" s="32" t="str">
         <f>IF(mesclun_crop_beds&gt;=mesclun_crop_cap-0.0001,"BINDING","SLACK")</f>
-        <v>SLACK</v>
+        <v>BINDING</v>
       </c>
       <c r="K9" s="32" t="str">
         <f>IF(mesclun_crop_beds&lt;=mesclun_crop_cap+0.0001,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="L9" s="33"/>
+      <c r="L9" s="33">
+        <v>246.48</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
@@ -10739,7 +10807,7 @@
       </c>
       <c r="I10" s="31">
         <f>temp_workers_needed</f>
-        <v>0</v>
+        <v>3.1647334126901998</v>
       </c>
       <c r="J10" s="32" t="str">
         <f>IF(temp_workers_needed&gt;=temp_max-0.0001,"BINDING","SLACK")</f>
@@ -10759,7 +10827,7 @@
       </c>
       <c r="B11" s="26">
         <f>tomato_crop_beds*tomato_crop_hrswk*season_weeks*(1+tomato_crop_dim)^tomato_crop_beds</f>
-        <v>0</v>
+        <v>2334.3682140900019</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -10771,7 +10839,7 @@
       </c>
       <c r="B12" s="26">
         <f>carrot_crop_beds*carrot_crop_hrswk*season_weeks*(1+carrot_crop_dim)^carrot_crop_beds</f>
-        <v>0</v>
+        <v>983.16986417423732</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
@@ -10786,7 +10854,7 @@
       </c>
       <c r="B13" s="26">
         <f>mesclun_crop_beds*mesclun_crop_hrswk*season_weeks*(1+mesclun_crop_dim)^mesclun_crop_beds</f>
-        <v>0</v>
+        <v>1959.6780360096488</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
@@ -10798,7 +10866,7 @@
       </c>
       <c r="B14" s="26">
         <f>mix_hrs_tomato+mix_hrs_carrot+mix_hrs_mesclun</f>
-        <v>0</v>
+        <v>5277.2161142738878</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -10810,7 +10878,7 @@
       </c>
       <c r="B15" s="26">
         <f>MIN(mix_hrs_total,farmer_hrs_field)</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="C15" t="s">
         <v>100</v>
@@ -10822,7 +10890,7 @@
       </c>
       <c r="B16" s="26">
         <f>mix_hrs_total-perm_hrs_used</f>
-        <v>0</v>
+        <v>4557.2161142738878</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
@@ -10834,7 +10902,7 @@
       </c>
       <c r="B17" s="27">
         <f>temp_hrs_used/temp_hrs_each</f>
-        <v>0</v>
+        <v>3.1647334126901998</v>
       </c>
       <c r="C17" t="s">
         <v>103</v>
@@ -10846,7 +10914,7 @@
       </c>
       <c r="B18" s="23">
         <f>perm_hrs_used*farmer_wage+temp_hrs_used*temp_wage</f>
-        <v>0</v>
+        <v>104118.335317255</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
@@ -10858,7 +10926,7 @@
       </c>
       <c r="B19" s="28">
         <f>IF(mix_hrs_total=0,0,labor_cost_total/mix_hrs_total)</f>
-        <v>0</v>
+        <v>19.729784239010844</v>
       </c>
       <c r="C19" t="s">
         <v>106</v>
@@ -10896,19 +10964,19 @@
       </c>
       <c r="B23" s="24">
         <f>tomato_crop_beds</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C23" s="24">
         <f>carrot_crop_beds</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D23" s="24">
         <f>mesclun_crop_beds</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E23" s="24">
         <f>SUM(mix_beds_row)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -10917,19 +10985,19 @@
       </c>
       <c r="B24" s="26">
         <f>mix_hrs_tomato</f>
-        <v>0</v>
+        <v>2334.3682140900019</v>
       </c>
       <c r="C24" s="26">
         <f>mix_hrs_carrot</f>
-        <v>0</v>
+        <v>983.16986417423732</v>
       </c>
       <c r="D24" s="26">
         <f>mix_hrs_mesclun</f>
-        <v>0</v>
+        <v>1959.6780360096488</v>
       </c>
       <c r="E24" s="26">
         <f>SUM(mix_hrs_row)</f>
-        <v>0</v>
+        <v>5277.2161142738878</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -10938,19 +11006,19 @@
       </c>
       <c r="B25" s="23">
         <f>tomato_crop_beds*tomato_crop_price</f>
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="C25" s="23">
         <f>carrot_crop_beds*carrot_crop_price</f>
-        <v>0</v>
+        <v>41880</v>
       </c>
       <c r="D25" s="23">
         <f>mesclun_crop_beds*mesclun_crop_price</f>
-        <v>0</v>
+        <v>81000</v>
       </c>
       <c r="E25" s="23">
         <f>SUM(mix_revenue_row)</f>
-        <v>0</v>
+        <v>210880</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -10959,19 +11027,19 @@
       </c>
       <c r="B26" s="23">
         <f>tomato_crop_beds*tomato_crop_fert</f>
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="C26" s="23">
         <f>carrot_crop_beds*carrot_crop_fert</f>
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D26" s="23">
         <f>mesclun_crop_beds*mesclun_crop_fert</f>
-        <v>0</v>
+        <v>26400</v>
       </c>
       <c r="E26" s="23">
         <f>SUM(mix_fert_row)</f>
-        <v>0</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -10980,19 +11048,19 @@
       </c>
       <c r="B27" s="23">
         <f>mix_hrs_tomato*labor_rate_blended</f>
-        <v>0</v>
+        <v>46056.581198400811</v>
       </c>
       <c r="C27" s="23">
         <f>mix_hrs_carrot*labor_rate_blended</f>
-        <v>0</v>
+        <v>19397.7292904553</v>
       </c>
       <c r="D27" s="23">
         <f>mix_hrs_mesclun*labor_rate_blended</f>
-        <v>0</v>
+        <v>38664.024828398891</v>
       </c>
       <c r="E27" s="23">
         <f>SUM(mix_labor_row)</f>
-        <v>0</v>
+        <v>104118.335317255</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -11001,19 +11069,19 @@
       </c>
       <c r="B28" s="23">
         <f>INDEX(mix_revenue_row,1)-INDEX(mix_fert_row,1)-INDEX(mix_labor_row,1)</f>
-        <v>0</v>
+        <v>33143.418801599189</v>
       </c>
       <c r="C28" s="23">
         <f>INDEX(mix_revenue_row,2)-INDEX(mix_fert_row,2)-INDEX(mix_labor_row,2)</f>
-        <v>0</v>
+        <v>13682.2707095447</v>
       </c>
       <c r="D28" s="23">
         <f>INDEX(mix_revenue_row,3)-INDEX(mix_fert_row,3)-INDEX(mix_labor_row,3)</f>
-        <v>0</v>
+        <v>15935.975171601109</v>
       </c>
       <c r="E28" s="23">
         <f>SUM(mix_contrib_row)</f>
-        <v>0</v>
+        <v>62761.664682745002</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -11031,7 +11099,7 @@
       </c>
       <c r="B31" s="23">
         <f>revenue_total</f>
-        <v>0</v>
+        <v>210880</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -11040,7 +11108,7 @@
       </c>
       <c r="B32" s="23">
         <f>fert_total</f>
-        <v>0</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -11049,7 +11117,7 @@
       </c>
       <c r="B33" s="23">
         <f>labor_cost_total</f>
-        <v>0</v>
+        <v>104118.335317255</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -11067,7 +11135,7 @@
       </c>
       <c r="B35" s="30">
         <f>revenue_total-fert_total-labor_cost_total-fixed_costs</f>
-        <v>-20000</v>
+        <v>42761.664682745002</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/allenmehr/Documents/GitHub/allen-mehr/capabilities/marginal-analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7278C96-8A4E-FC47-9D8A-A1067E752D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680489E5-7BD4-9549-9F20-6A1AFD7C496A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20420" activeTab="3" xr2:uid="{BDFB547A-7CF5-5D46-A116-A51B8B0DF0D0}"/>
   </bookViews>
